--- a/image manifest.xlsx
+++ b/image manifest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Github\CS-Graphics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25D82F9-170E-414E-ADAD-D9E4B0663ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890FBC49-6F10-4CE1-8407-38AFAD25E180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{620D0F7A-D0D3-4EA0-8A4D-C0BB25CE06A6}"/>
+    <workbookView xWindow="3780" yWindow="2415" windowWidth="21600" windowHeight="12795" xr2:uid="{620D0F7A-D0D3-4EA0-8A4D-C0BB25CE06A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8774" uniqueCount="1424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9378" uniqueCount="1495">
   <si>
     <t>Filename</t>
   </si>
@@ -4313,6 +4313,219 @@
   </si>
   <si>
     <t>name(TODO) idle danger</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>Game credits</t>
+  </si>
+  <si>
+    <t>HERC unlock (Sensei, Giant, Ogre)</t>
+  </si>
+  <si>
+    <t>HERC unlock (Reaper)</t>
+  </si>
+  <si>
+    <t>Background HERC bay</t>
+  </si>
+  <si>
+    <t>Unkown</t>
+  </si>
+  <si>
+    <t>Blink (1fps)</t>
+  </si>
+  <si>
+    <t>Error? (1fps)</t>
+  </si>
+  <si>
+    <t>Blink (3fps)</t>
+  </si>
+  <si>
+    <t>Blink (15fps)</t>
+  </si>
+  <si>
+    <t>Error? (15fps)</t>
+  </si>
+  <si>
+    <t>HERCbay spotlight on</t>
+  </si>
+  <si>
+    <t>HERCbay idle</t>
+  </si>
+  <si>
+    <t>HERCbay grid on</t>
+  </si>
+  <si>
+    <t>Carrier landing</t>
+  </si>
+  <si>
+    <t>HERC unlock (Demon)</t>
+  </si>
+  <si>
+    <t>HERC unlock (Juggernaut)</t>
+  </si>
+  <si>
+    <t>Player death start</t>
+  </si>
+  <si>
+    <t>Player death idle</t>
+  </si>
+  <si>
+    <t>Player death end</t>
+  </si>
+  <si>
+    <t>Biovat idle</t>
+  </si>
+  <si>
+    <t>Biovat start</t>
+  </si>
+  <si>
+    <t>Bioderm name(TODO) unlock</t>
+  </si>
+  <si>
+    <t>Multiplayer background</t>
+  </si>
+  <si>
+    <t>Intro Cybrid(TODO)</t>
+  </si>
+  <si>
+    <t>Intro Unitech Demon</t>
+  </si>
+  <si>
+    <t>Intro Unitech Reaper</t>
+  </si>
+  <si>
+    <t>Intro Unitech Giant</t>
+  </si>
+  <si>
+    <t>Intro Cybrid Hades</t>
+  </si>
+  <si>
+    <t>Intro Unitech Ogre</t>
+  </si>
+  <si>
+    <t>Intro Unitech Remora</t>
+  </si>
+  <si>
+    <t>Intro Unitech Sensei</t>
+  </si>
+  <si>
+    <t>Intro Unitech Shadow</t>
+  </si>
+  <si>
+    <t>Promotion 1</t>
+  </si>
+  <si>
+    <t>Promotion 2</t>
+  </si>
+  <si>
+    <t>Promotion 3</t>
+  </si>
+  <si>
+    <t>Promotion 4</t>
+  </si>
+  <si>
+    <t>Promotion 5</t>
+  </si>
+  <si>
+    <t>Promotion 6</t>
+  </si>
+  <si>
+    <t>Promotion 7</t>
+  </si>
+  <si>
+    <t>Promotion 8</t>
+  </si>
+  <si>
+    <t>Promotion 9</t>
+  </si>
+  <si>
+    <t>Promotion 10</t>
+  </si>
+  <si>
+    <t>Promotion 11</t>
+  </si>
+  <si>
+    <t>Promotion 12</t>
+  </si>
+  <si>
+    <t>Promotion 13</t>
+  </si>
+  <si>
+    <t>Promotion 14</t>
+  </si>
+  <si>
+    <t>Bioderm facility overview</t>
+  </si>
+  <si>
+    <t>HERC unlock (Remora, Shadow)</t>
+  </si>
+  <si>
+    <t>Link idle</t>
+  </si>
+  <si>
+    <t>Link start</t>
+  </si>
+  <si>
+    <t>HERC unlock?</t>
+  </si>
+  <si>
+    <t>Tutorial 2 TODO</t>
+  </si>
+  <si>
+    <t>Tutorial 3</t>
+  </si>
+  <si>
+    <t>Tutorial 4</t>
+  </si>
+  <si>
+    <t>Tutorial 5</t>
+  </si>
+  <si>
+    <t>Tutorial 6</t>
+  </si>
+  <si>
+    <t>Tutorial 7</t>
+  </si>
+  <si>
+    <t>Tutorial 8</t>
+  </si>
+  <si>
+    <t>Tutorial 9</t>
+  </si>
+  <si>
+    <t>Tutorial 10</t>
+  </si>
+  <si>
+    <t>Biovat end</t>
+  </si>
+  <si>
+    <t>VR end</t>
+  </si>
+  <si>
+    <t>VR start</t>
+  </si>
+  <si>
+    <t>VR idle</t>
+  </si>
+  <si>
+    <t>Carrier flyby</t>
+  </si>
+  <si>
+    <t>Ending 1</t>
+  </si>
+  <si>
+    <t>Ending 4</t>
+  </si>
+  <si>
+    <t>Ending 3</t>
+  </si>
+  <si>
+    <t>Ending 2</t>
+  </si>
+  <si>
+    <t>Tutorial 1 TODO (fixed)</t>
   </si>
 </sst>
 </file>
@@ -4379,7 +4592,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="User" refreshedDate="46273.541146875003" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1160" xr:uid="{475285A3-2F52-4B23-B5E6-6919749F1CF6}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="User" refreshedDate="46273.60544201389" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1160" xr:uid="{475285A3-2F52-4B23-B5E6-6919749F1CF6}">
   <cacheSource type="worksheet">
     <worksheetSource name="Table1"/>
   </cacheSource>
@@ -4403,7 +4616,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Frames" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="636"/>
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1801"/>
     </cacheField>
     <cacheField name="Animation stacked" numFmtId="0">
       <sharedItems containsBlank="1"/>
@@ -18128,7 +18341,7 @@
     <x v="4"/>
     <n v="113401"/>
     <m/>
-    <m/>
+    <s v="Palette"/>
     <m/>
     <m/>
     <m/>
@@ -18140,13 +18353,13 @@
     <s v="BRAIN2.FLX"/>
     <x v="4"/>
     <n v="1104621"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Bioderm name(TODO) unlock"/>
     <m/>
   </r>
   <r>
@@ -18154,7 +18367,7 @@
     <x v="4"/>
     <n v="82563"/>
     <m/>
-    <m/>
+    <s v="Error"/>
     <m/>
     <m/>
     <m/>
@@ -18166,39 +18379,39 @@
     <s v="CREDITS.FLX"/>
     <x v="4"/>
     <n v="4969437"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="1801"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Game credits"/>
     <m/>
   </r>
   <r>
     <s v="DEFENDER.FLX"/>
     <x v="4"/>
     <n v="2026180"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="121"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="HERC unlock (Sensei, Giant, Ogre)"/>
     <m/>
   </r>
   <r>
     <s v="DESTROY.FLX"/>
     <x v="4"/>
     <n v="691774"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="121"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="HERC unlock (Reaper)"/>
     <m/>
   </r>
   <r>
@@ -18206,7 +18419,7 @@
     <x v="4"/>
     <n v="732108"/>
     <m/>
-    <m/>
+    <s v="Palette"/>
     <m/>
     <m/>
     <m/>
@@ -18218,364 +18431,364 @@
     <s v="HBASE.FLX"/>
     <x v="4"/>
     <n v="99738"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="32"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Background HERC bay"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB1.FLX"/>
     <x v="4"/>
     <n v="405"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="5"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Error? (1fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB10.FLX"/>
     <x v="4"/>
     <n v="569"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="6"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Blink (1fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB11.FLX"/>
     <x v="4"/>
     <n v="538"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="6"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Blink (1fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB12.FLX"/>
     <x v="4"/>
     <n v="538"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="6"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Blink (1fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB13.FLX"/>
     <x v="4"/>
     <n v="526"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="6"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Blink (1fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB14.FLX"/>
     <x v="4"/>
     <n v="535"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="6"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Blink (1fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB15.FLX"/>
     <x v="4"/>
     <n v="526"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="6"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Blink (1fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB16.FLX"/>
     <x v="4"/>
     <n v="495"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="6"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Error? (1fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB17.FLX"/>
     <x v="4"/>
     <n v="800"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="10"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Blink (3fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB18.FLX"/>
     <x v="4"/>
     <n v="1282"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="10"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Blink (15fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB2.FLX"/>
     <x v="4"/>
     <n v="532"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="7"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Blink (1fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB3.FLX"/>
     <x v="4"/>
     <n v="477"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="6"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Error? (1fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB4.FLX"/>
     <x v="4"/>
     <n v="412"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="5"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Error? (1fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB5.FLX"/>
     <x v="4"/>
     <n v="431"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="5"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Error? (1fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB6.FLX"/>
     <x v="4"/>
     <n v="478"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="6"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Error? (1fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB7.FLX"/>
     <x v="4"/>
     <n v="484"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="6"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Error? (15fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB8.FLX"/>
     <x v="4"/>
     <n v="498"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="6"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Blink (1fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_AMB9.FLX"/>
     <x v="4"/>
     <n v="484"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="6"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Unkown"/>
+    <s v="Error? (1fps)"/>
     <m/>
   </r>
   <r>
     <s v="HB_BUY.FLX"/>
     <x v="4"/>
     <n v="138349"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="14"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="HERCbay spotlight on"/>
     <m/>
   </r>
   <r>
     <s v="HB_IDLE.FLX"/>
     <x v="4"/>
     <n v="65807"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="27"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="HERCbay idle"/>
     <m/>
   </r>
   <r>
     <s v="HB_UPG.FLX"/>
     <x v="4"/>
     <n v="450299"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="32"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="HERCbay grid on"/>
     <m/>
   </r>
   <r>
     <s v="ICEMOON.FLX"/>
     <x v="4"/>
     <n v="176640"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="8"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Carrier landing"/>
     <m/>
   </r>
   <r>
     <s v="INVADER.FLX"/>
     <x v="4"/>
     <n v="1145237"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="HERC unlock (Demon)"/>
     <m/>
   </r>
   <r>
     <s v="JUGGERN.FLX"/>
     <x v="4"/>
     <n v="897868"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="121"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="HERC unlock (Juggernaut)"/>
     <m/>
   </r>
   <r>
     <s v="LOSER4A.FLX"/>
     <x v="4"/>
     <n v="191432"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="16"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Player death start"/>
     <m/>
   </r>
   <r>
     <s v="LOSER4B.FLX"/>
     <x v="4"/>
     <n v="66520"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="21"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Player death idle"/>
     <m/>
   </r>
   <r>
     <s v="LOSER4C.FLX"/>
     <x v="4"/>
     <n v="2760740"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="421"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Player death end"/>
     <m/>
   </r>
   <r>
@@ -18583,7 +18796,7 @@
     <x v="4"/>
     <n v="364284"/>
     <m/>
-    <m/>
+    <s v="Palette"/>
     <m/>
     <m/>
     <m/>
@@ -18595,507 +18808,507 @@
     <s v="MLLOOP.FLX"/>
     <x v="4"/>
     <n v="228640"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="32"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Biovat idle"/>
     <m/>
   </r>
   <r>
     <s v="MLSTART.FLX"/>
     <x v="4"/>
     <n v="352649"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="32"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Biovat start"/>
     <m/>
   </r>
   <r>
     <s v="MONK.FLX"/>
     <x v="4"/>
     <n v="3372255"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Bioderm name(TODO) unlock"/>
     <m/>
   </r>
   <r>
     <s v="MPLBG.FLX"/>
     <x v="4"/>
     <n v="58575"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="113"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Multiplayer background"/>
     <m/>
   </r>
   <r>
     <s v="OGRE_ETC.FLX"/>
     <x v="4"/>
     <n v="718664"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="HERC unlock (Sensei, Giant, Ogre)"/>
     <m/>
   </r>
   <r>
     <s v="OM3A.FLX"/>
     <x v="4"/>
     <n v="2552017"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Bioderm name(TODO) unlock"/>
     <m/>
   </r>
   <r>
     <s v="OM4A.FLX"/>
     <x v="4"/>
     <n v="2764400"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Bioderm name(TODO) unlock"/>
     <m/>
   </r>
   <r>
     <s v="PRE_ARAC.FLX"/>
     <x v="4"/>
     <n v="533473"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="49"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Cybrid(TODO)"/>
     <m/>
   </r>
   <r>
     <s v="PRE_CERE.FLX"/>
     <x v="4"/>
     <n v="1437424"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="49"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Cybrid(TODO)"/>
     <m/>
   </r>
   <r>
     <s v="PRE_DEFN.FLX"/>
     <x v="4"/>
     <n v="1104204"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="49"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Unitech Demon"/>
     <m/>
   </r>
   <r>
     <s v="PRE_DEST.FLX"/>
     <x v="4"/>
     <n v="1597432"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="49"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Unitech Reaper"/>
     <m/>
   </r>
   <r>
     <s v="PRE_GEN.FLX"/>
     <x v="4"/>
     <n v="1107679"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="49"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Cybrid(TODO)"/>
     <m/>
   </r>
   <r>
     <s v="PRE_GIAN.FLX"/>
     <x v="4"/>
     <n v="1244832"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="49"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Unitech Giant"/>
     <m/>
   </r>
   <r>
     <s v="PRE_HAD.FLX"/>
     <x v="4"/>
     <n v="1147126"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="49"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Cybrid Hades"/>
     <m/>
   </r>
   <r>
     <s v="PRE_JUGG.FLX"/>
     <x v="4"/>
     <n v="1231072"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="43"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Unitech Giant"/>
     <m/>
   </r>
   <r>
     <s v="PRE_MALI.FLX"/>
     <x v="4"/>
     <n v="312545"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="26"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Cybrid(TODO)"/>
     <m/>
   </r>
   <r>
     <s v="PRE_NIH.FLX"/>
     <x v="4"/>
     <n v="933591"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="49"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Cybrid(TODO)"/>
     <m/>
   </r>
   <r>
     <s v="PRE_OGRE.FLX"/>
     <x v="4"/>
     <n v="1002169"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="50"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Unitech Ogre"/>
     <m/>
   </r>
   <r>
     <s v="PRE_PARA.FLX"/>
     <x v="4"/>
     <n v="802464"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="43"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Cybrid(TODO)"/>
     <m/>
   </r>
   <r>
     <s v="PRE_REMO.FLX"/>
     <x v="4"/>
     <n v="336637"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="25"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Unitech Remora"/>
     <m/>
   </r>
   <r>
     <s v="PRE_SENS.FLX"/>
     <x v="4"/>
     <n v="414191"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="24"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Unitech Sensei"/>
     <m/>
   </r>
   <r>
     <s v="PRE_SHAD.FLX"/>
     <x v="4"/>
     <n v="666111"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="49"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Unitech Shadow"/>
     <m/>
   </r>
   <r>
     <s v="PRE_SPE.FLX"/>
     <x v="4"/>
     <n v="787797"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="49"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Intro Cybrid(TODO)"/>
     <m/>
   </r>
   <r>
     <s v="PROMO1.FLX"/>
     <x v="4"/>
     <n v="184250"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Promotion 1"/>
     <m/>
   </r>
   <r>
     <s v="PROMO10.FLX"/>
     <x v="4"/>
     <n v="115916"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="90"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Promotion 10"/>
     <m/>
   </r>
   <r>
     <s v="PROMO11.FLX"/>
     <x v="4"/>
     <n v="114355"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="90"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Promotion 11"/>
     <m/>
   </r>
   <r>
     <s v="PROMO12.FLX"/>
     <x v="4"/>
     <n v="103966"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="92"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Promotion 12"/>
     <m/>
   </r>
   <r>
     <s v="PROMO13.FLX"/>
     <x v="4"/>
     <n v="102173"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="92"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Promotion 13"/>
     <m/>
   </r>
   <r>
     <s v="PROMO14.FLX"/>
     <x v="4"/>
     <n v="134907"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Promotion 14"/>
     <m/>
   </r>
   <r>
     <s v="PROMO2.FLX"/>
     <x v="4"/>
     <n v="119395"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Promotion 2"/>
     <m/>
   </r>
   <r>
     <s v="PROMO3.FLX"/>
     <x v="4"/>
     <n v="121414"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Promotion 3"/>
     <m/>
   </r>
   <r>
     <s v="PROMO4.FLX"/>
     <x v="4"/>
     <n v="119931"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="90"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Promotion 4"/>
     <m/>
   </r>
   <r>
     <s v="PROMO5.FLX"/>
     <x v="4"/>
     <n v="119931"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="90"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Promotion 5"/>
     <m/>
   </r>
   <r>
     <s v="PROMO6.FLX"/>
     <x v="4"/>
     <n v="123991"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="90"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Promotion 6"/>
     <m/>
   </r>
   <r>
     <s v="PROMO7.FLX"/>
     <x v="4"/>
     <n v="121192"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="90"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Promotion 7"/>
     <m/>
   </r>
   <r>
     <s v="PROMO8.FLX"/>
     <x v="4"/>
     <n v="120272"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="90"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Promotion 8"/>
     <m/>
   </r>
   <r>
     <s v="PROMO9.FLX"/>
     <x v="4"/>
     <n v="118439"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="90"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Promotion 9"/>
     <m/>
   </r>
   <r>
     <s v="PROTOS.FLX"/>
     <x v="4"/>
     <n v="922116"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Bioderm facility overview"/>
     <m/>
   </r>
   <r>
     <s v="REM_SHAD.FLX"/>
     <x v="4"/>
     <n v="380503"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="HERC unlock (Remora, Shadow)"/>
     <m/>
   </r>
   <r>
@@ -19103,7 +19316,7 @@
     <x v="4"/>
     <n v="241337"/>
     <m/>
-    <m/>
+    <s v="Palette"/>
     <m/>
     <m/>
     <m/>
@@ -19115,26 +19328,26 @@
     <s v="SBLOOP.FLX"/>
     <x v="4"/>
     <n v="233715"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="33"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Link idle"/>
     <m/>
   </r>
   <r>
     <s v="SBSTART.FLX"/>
     <x v="4"/>
     <n v="232871"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="33"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Link start"/>
     <m/>
   </r>
   <r>
@@ -19142,7 +19355,7 @@
     <x v="4"/>
     <n v="419334"/>
     <m/>
-    <m/>
+    <s v="Palette"/>
     <m/>
     <m/>
     <m/>
@@ -19154,182 +19367,182 @@
     <s v="TECH0.FLX"/>
     <x v="4"/>
     <n v="380503"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="HERC unlock (Remora, Shadow)"/>
     <m/>
   </r>
   <r>
     <s v="TECH1.FLX"/>
     <x v="4"/>
     <n v="269577"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="121"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="HERC unlock?"/>
     <m/>
   </r>
   <r>
     <s v="TUTOR3A.FLX"/>
     <x v="4"/>
     <n v="1328484"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="1001"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Tutorial 1 TODO"/>
     <m/>
   </r>
   <r>
     <s v="TUTOR3B.FLX"/>
     <x v="4"/>
     <n v="2402745"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="1501"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Tutorial 2 TODO"/>
     <m/>
   </r>
   <r>
     <s v="TUTOR3C.FLX"/>
     <x v="4"/>
     <n v="4153928"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="484"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Tutorial 3"/>
     <m/>
   </r>
   <r>
     <s v="TUTOR3D.FLX"/>
     <x v="4"/>
     <n v="212960"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="41"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Tutorial 4"/>
     <m/>
   </r>
   <r>
     <s v="TUTOR3E.FLX"/>
     <x v="4"/>
     <n v="175772"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="41"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Tutorial 5"/>
     <m/>
   </r>
   <r>
     <s v="TUTOR3F.FLX"/>
     <x v="4"/>
     <n v="205204"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="41"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Tutorial 6"/>
     <m/>
   </r>
   <r>
     <s v="TUTOR3G.FLX"/>
     <x v="4"/>
     <n v="315850"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="41"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Tutorial 7"/>
     <m/>
   </r>
   <r>
     <s v="TUTOR3H.FLX"/>
     <x v="4"/>
     <n v="360127"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="41"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Tutorial 8"/>
     <m/>
   </r>
   <r>
     <s v="TUTOR3I.FLX"/>
     <x v="4"/>
     <n v="78162"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="41"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Tutorial 9"/>
     <m/>
   </r>
   <r>
     <s v="TUTOR3J.FLX"/>
     <x v="4"/>
     <n v="1911"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="21"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Tutorial 10"/>
     <m/>
   </r>
   <r>
     <s v="VATDOOR.FLX"/>
     <x v="4"/>
     <n v="192819"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Biovat start"/>
     <m/>
   </r>
   <r>
     <s v="VATLOOP.FLX"/>
     <x v="4"/>
     <n v="140076"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="32"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Biovat idle"/>
     <m/>
   </r>
   <r>
@@ -19337,12 +19550,12 @@
     <x v="4"/>
     <n v="198828"/>
     <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Palette"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Biovat end"/>
     <m/>
   </r>
   <r>
@@ -19350,168 +19563,168 @@
     <x v="4"/>
     <n v="495086"/>
     <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="Palette"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="VR end"/>
     <m/>
   </r>
   <r>
     <s v="VRLOOP.FLX"/>
     <x v="4"/>
     <n v="129154"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="33"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="VR idle"/>
     <m/>
   </r>
   <r>
     <s v="VRSTART.FLX"/>
     <x v="4"/>
     <n v="481034"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="33"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="VR start"/>
     <m/>
   </r>
   <r>
     <s v="WF1A.FLX"/>
     <x v="4"/>
     <n v="1578016"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Bioderm name(TODO) unlock"/>
     <m/>
   </r>
   <r>
     <s v="WHOOSH.FLX"/>
     <x v="4"/>
     <n v="1879615"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="62"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Carrier flyby"/>
     <m/>
   </r>
   <r>
     <s v="WINNINGA.FLX"/>
     <x v="4"/>
     <n v="5619883"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="393"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Ending 1"/>
     <m/>
   </r>
   <r>
     <s v="WINNINGB.FLX"/>
     <x v="4"/>
     <n v="1466510"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="61"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Ending 2"/>
     <m/>
   </r>
   <r>
     <s v="WINNINGC.FLX"/>
     <x v="4"/>
     <n v="2982483"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="200"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Ending 3"/>
     <m/>
   </r>
   <r>
     <s v="WINNINGD.FLX"/>
     <x v="4"/>
     <n v="1247919"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="92"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Ending 4"/>
     <m/>
   </r>
   <r>
     <s v="WM6A.FLX"/>
     <x v="4"/>
     <n v="3099362"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Bioderm name(TODO) unlock"/>
     <m/>
   </r>
   <r>
     <s v="WM7A.FLX"/>
     <x v="4"/>
     <n v="3208052"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Bioderm name(TODO) unlock"/>
     <m/>
   </r>
   <r>
     <s v="WM8A.FLX"/>
     <x v="4"/>
     <n v="1477350"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Bioderm name(TODO) unlock"/>
     <m/>
   </r>
   <r>
     <s v="WM9A.FLX"/>
     <x v="4"/>
     <n v="2327897"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
+    <s v="SELF"/>
+    <n v="91"/>
+    <s v="Yes"/>
+    <s v="No"/>
+    <s v="No"/>
+    <s v="Video"/>
+    <s v="Bioderm name(TODO) unlock"/>
     <m/>
   </r>
 </pivotCacheRecords>
@@ -54020,6 +54233,9 @@
       <c r="C1055" s="4">
         <v>113401</v>
       </c>
+      <c r="E1055" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="1056" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
@@ -54031,8 +54247,29 @@
       <c r="C1056" s="4">
         <v>1104621</v>
       </c>
-    </row>
-    <row r="1057" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1056" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1056">
+        <v>91</v>
+      </c>
+      <c r="F1056" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1056" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1056" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1056" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1056" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
         <v>1304</v>
       </c>
@@ -54042,8 +54279,11 @@
       <c r="C1057" s="4">
         <v>82563</v>
       </c>
-    </row>
-    <row r="1058" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E1057" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
         <v>1305</v>
       </c>
@@ -54053,8 +54293,29 @@
       <c r="C1058" s="4">
         <v>4969437</v>
       </c>
-    </row>
-    <row r="1059" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1058" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1058">
+        <v>1801</v>
+      </c>
+      <c r="F1058" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1058" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1058" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1058" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1058" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
         <v>1306</v>
       </c>
@@ -54064,8 +54325,29 @@
       <c r="C1059" s="4">
         <v>2026180</v>
       </c>
-    </row>
-    <row r="1060" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1059" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1059">
+        <v>121</v>
+      </c>
+      <c r="F1059" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1059" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1059" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1059" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1059" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
         <v>1307</v>
       </c>
@@ -54075,8 +54357,29 @@
       <c r="C1060" s="4">
         <v>691774</v>
       </c>
-    </row>
-    <row r="1061" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1060" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1060">
+        <v>121</v>
+      </c>
+      <c r="F1060" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1060" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1060" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1060" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1060" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
         <v>1308</v>
       </c>
@@ -54086,8 +54389,11 @@
       <c r="C1061" s="4">
         <v>732108</v>
       </c>
-    </row>
-    <row r="1062" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E1061" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
         <v>1309</v>
       </c>
@@ -54097,8 +54403,29 @@
       <c r="C1062" s="4">
         <v>99738</v>
       </c>
-    </row>
-    <row r="1063" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1062" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1062">
+        <v>32</v>
+      </c>
+      <c r="F1062" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1062" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1062" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1062" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1062" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
         <v>1310</v>
       </c>
@@ -54108,8 +54435,29 @@
       <c r="C1063" s="4">
         <v>405</v>
       </c>
-    </row>
-    <row r="1064" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1063" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1063">
+        <v>5</v>
+      </c>
+      <c r="F1063" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1063" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1063" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1063" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1063" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1064" t="s">
         <v>1311</v>
       </c>
@@ -54119,8 +54467,29 @@
       <c r="C1064" s="4">
         <v>569</v>
       </c>
-    </row>
-    <row r="1065" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1064" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1064">
+        <v>6</v>
+      </c>
+      <c r="F1064" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1064" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1064" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1064" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1064" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1065" t="s">
         <v>1312</v>
       </c>
@@ -54130,8 +54499,29 @@
       <c r="C1065" s="4">
         <v>538</v>
       </c>
-    </row>
-    <row r="1066" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1065" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1065">
+        <v>6</v>
+      </c>
+      <c r="F1065" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1065" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1065" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1065" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1065" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1066" t="s">
         <v>1313</v>
       </c>
@@ -54141,8 +54531,29 @@
       <c r="C1066" s="4">
         <v>538</v>
       </c>
-    </row>
-    <row r="1067" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1066" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1066">
+        <v>6</v>
+      </c>
+      <c r="F1066" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1066" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1066" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1066" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1066" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1067" t="s">
         <v>1314</v>
       </c>
@@ -54152,8 +54563,29 @@
       <c r="C1067" s="4">
         <v>526</v>
       </c>
-    </row>
-    <row r="1068" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1067" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1067">
+        <v>6</v>
+      </c>
+      <c r="F1067" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1067" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1067" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1067" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1067" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1068" t="s">
         <v>1315</v>
       </c>
@@ -54163,8 +54595,29 @@
       <c r="C1068" s="4">
         <v>535</v>
       </c>
-    </row>
-    <row r="1069" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1068" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1068">
+        <v>6</v>
+      </c>
+      <c r="F1068" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1068" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1068" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1068" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1068" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1069" t="s">
         <v>1316</v>
       </c>
@@ -54174,8 +54627,29 @@
       <c r="C1069" s="4">
         <v>526</v>
       </c>
-    </row>
-    <row r="1070" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1069" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1069">
+        <v>6</v>
+      </c>
+      <c r="F1069" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1069" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1069" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1069" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1069" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1070" t="s">
         <v>1317</v>
       </c>
@@ -54185,8 +54659,29 @@
       <c r="C1070" s="4">
         <v>495</v>
       </c>
-    </row>
-    <row r="1071" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1070" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1070">
+        <v>6</v>
+      </c>
+      <c r="F1070" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1070" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1070" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1070" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1070" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1071" t="s">
         <v>1318</v>
       </c>
@@ -54196,8 +54691,29 @@
       <c r="C1071" s="4">
         <v>800</v>
       </c>
-    </row>
-    <row r="1072" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1071" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1071">
+        <v>10</v>
+      </c>
+      <c r="F1071" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1071" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1071" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1071" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1071" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1072" t="s">
         <v>1319</v>
       </c>
@@ -54207,8 +54723,29 @@
       <c r="C1072" s="4">
         <v>1282</v>
       </c>
-    </row>
-    <row r="1073" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1072" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1072">
+        <v>10</v>
+      </c>
+      <c r="F1072" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1072" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1072" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1072" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1072" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1073" t="s">
         <v>1320</v>
       </c>
@@ -54218,8 +54755,29 @@
       <c r="C1073" s="4">
         <v>532</v>
       </c>
-    </row>
-    <row r="1074" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1073" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1073">
+        <v>7</v>
+      </c>
+      <c r="F1073" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1073" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1073" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1073" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1073" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1074" t="s">
         <v>1321</v>
       </c>
@@ -54229,8 +54787,29 @@
       <c r="C1074" s="4">
         <v>477</v>
       </c>
-    </row>
-    <row r="1075" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1074" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1074">
+        <v>6</v>
+      </c>
+      <c r="F1074" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1074" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1074" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1074" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1074" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1075" t="s">
         <v>1322</v>
       </c>
@@ -54240,8 +54819,29 @@
       <c r="C1075" s="4">
         <v>412</v>
       </c>
-    </row>
-    <row r="1076" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1075" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1075">
+        <v>5</v>
+      </c>
+      <c r="F1075" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1075" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1075" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1075" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1075" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1076" t="s">
         <v>1323</v>
       </c>
@@ -54251,8 +54851,29 @@
       <c r="C1076" s="4">
         <v>431</v>
       </c>
-    </row>
-    <row r="1077" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1076" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1076">
+        <v>5</v>
+      </c>
+      <c r="F1076" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1076" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1076" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1076" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1076" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1077" t="s">
         <v>1324</v>
       </c>
@@ -54262,8 +54883,29 @@
       <c r="C1077" s="4">
         <v>478</v>
       </c>
-    </row>
-    <row r="1078" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1077" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1077">
+        <v>6</v>
+      </c>
+      <c r="F1077" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1077" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1077" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1077" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1077" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1078" t="s">
         <v>1325</v>
       </c>
@@ -54273,8 +54915,29 @@
       <c r="C1078" s="4">
         <v>484</v>
       </c>
-    </row>
-    <row r="1079" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1078" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1078">
+        <v>6</v>
+      </c>
+      <c r="F1078" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1078" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1078" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1078" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1078" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1079" t="s">
         <v>1326</v>
       </c>
@@ -54284,8 +54947,29 @@
       <c r="C1079" s="4">
         <v>498</v>
       </c>
-    </row>
-    <row r="1080" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1079" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1079">
+        <v>6</v>
+      </c>
+      <c r="F1079" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1079" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1079" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1079" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1079" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1080" t="s">
         <v>1327</v>
       </c>
@@ -54295,8 +54979,29 @@
       <c r="C1080" s="4">
         <v>484</v>
       </c>
-    </row>
-    <row r="1081" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1080" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1080">
+        <v>6</v>
+      </c>
+      <c r="F1080" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1080" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1080" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1080" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J1080" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
         <v>1328</v>
       </c>
@@ -54306,8 +55011,29 @@
       <c r="C1081" s="4">
         <v>138349</v>
       </c>
-    </row>
-    <row r="1082" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1081" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1081">
+        <v>14</v>
+      </c>
+      <c r="F1081" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1081" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1081" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1081" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1081" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1082" t="s">
         <v>1329</v>
       </c>
@@ -54317,8 +55043,29 @@
       <c r="C1082" s="4">
         <v>65807</v>
       </c>
-    </row>
-    <row r="1083" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1082" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1082">
+        <v>27</v>
+      </c>
+      <c r="F1082" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1082" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1082" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1082" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1082" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
         <v>1330</v>
       </c>
@@ -54328,8 +55075,29 @@
       <c r="C1083" s="4">
         <v>450299</v>
       </c>
-    </row>
-    <row r="1084" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1083" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1083">
+        <v>32</v>
+      </c>
+      <c r="F1083" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1083" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1083" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1083" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1083" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
         <v>1331</v>
       </c>
@@ -54339,8 +55107,29 @@
       <c r="C1084" s="4">
         <v>176640</v>
       </c>
-    </row>
-    <row r="1085" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1084" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1084">
+        <v>8</v>
+      </c>
+      <c r="F1084" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1084" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1084" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1084" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1084" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1085" t="s">
         <v>1332</v>
       </c>
@@ -54350,8 +55139,29 @@
       <c r="C1085" s="4">
         <v>1145237</v>
       </c>
-    </row>
-    <row r="1086" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1085" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1085">
+        <v>91</v>
+      </c>
+      <c r="F1085" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1085" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1085" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1085" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1085" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1086" t="s">
         <v>1333</v>
       </c>
@@ -54361,8 +55171,29 @@
       <c r="C1086" s="4">
         <v>897868</v>
       </c>
-    </row>
-    <row r="1087" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1086" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1086">
+        <v>121</v>
+      </c>
+      <c r="F1086" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1086" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1086" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1086" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1086" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1087" t="s">
         <v>1334</v>
       </c>
@@ -54372,8 +55203,29 @@
       <c r="C1087" s="4">
         <v>191432</v>
       </c>
-    </row>
-    <row r="1088" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1087" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1087">
+        <v>16</v>
+      </c>
+      <c r="F1087" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1087" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1087" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1087" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1087" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
         <v>1335</v>
       </c>
@@ -54383,8 +55235,29 @@
       <c r="C1088" s="4">
         <v>66520</v>
       </c>
-    </row>
-    <row r="1089" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1088" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1088">
+        <v>21</v>
+      </c>
+      <c r="F1088" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1088" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1088" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1088" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1088" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1089" t="s">
         <v>1336</v>
       </c>
@@ -54394,8 +55267,29 @@
       <c r="C1089" s="4">
         <v>2760740</v>
       </c>
-    </row>
-    <row r="1090" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1089" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1089">
+        <v>421</v>
+      </c>
+      <c r="F1089" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1089" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1089" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1089" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1089" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1090" t="s">
         <v>1337</v>
       </c>
@@ -54405,8 +55299,11 @@
       <c r="C1090" s="4">
         <v>364284</v>
       </c>
-    </row>
-    <row r="1091" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E1090" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1091" t="s">
         <v>1338</v>
       </c>
@@ -54416,8 +55313,29 @@
       <c r="C1091" s="4">
         <v>228640</v>
       </c>
-    </row>
-    <row r="1092" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1091" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1091">
+        <v>32</v>
+      </c>
+      <c r="F1091" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1091" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1091" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1091" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1091" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1092" t="s">
         <v>1339</v>
       </c>
@@ -54427,8 +55345,29 @@
       <c r="C1092" s="4">
         <v>352649</v>
       </c>
-    </row>
-    <row r="1093" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1092" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1092">
+        <v>32</v>
+      </c>
+      <c r="F1092" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1092" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1092" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1092" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1092" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1093" t="s">
         <v>1340</v>
       </c>
@@ -54438,8 +55377,29 @@
       <c r="C1093" s="4">
         <v>3372255</v>
       </c>
-    </row>
-    <row r="1094" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1093" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1093">
+        <v>91</v>
+      </c>
+      <c r="F1093" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1093" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1093" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1093" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1093" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1094" t="s">
         <v>1341</v>
       </c>
@@ -54449,8 +55409,29 @@
       <c r="C1094" s="4">
         <v>58575</v>
       </c>
-    </row>
-    <row r="1095" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1094" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1094">
+        <v>113</v>
+      </c>
+      <c r="F1094" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1094" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1094" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1094" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1094" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1095" t="s">
         <v>1342</v>
       </c>
@@ -54460,8 +55441,29 @@
       <c r="C1095" s="4">
         <v>718664</v>
       </c>
-    </row>
-    <row r="1096" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1095" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1095">
+        <v>91</v>
+      </c>
+      <c r="F1095" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1095" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1095" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1095" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1095" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1096" t="s">
         <v>1343</v>
       </c>
@@ -54471,8 +55473,29 @@
       <c r="C1096" s="4">
         <v>2552017</v>
       </c>
-    </row>
-    <row r="1097" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1096" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1096">
+        <v>91</v>
+      </c>
+      <c r="F1096" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1096" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1096" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1096" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1096" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1097" t="s">
         <v>1344</v>
       </c>
@@ -54482,8 +55505,29 @@
       <c r="C1097" s="4">
         <v>2764400</v>
       </c>
-    </row>
-    <row r="1098" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1097" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1097">
+        <v>91</v>
+      </c>
+      <c r="F1097" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1097" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1097" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1097" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1097" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1098" t="s">
         <v>1345</v>
       </c>
@@ -54493,8 +55537,29 @@
       <c r="C1098" s="4">
         <v>533473</v>
       </c>
-    </row>
-    <row r="1099" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1098" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1098">
+        <v>49</v>
+      </c>
+      <c r="F1098" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1098" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1098" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1098" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1098" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1099" t="s">
         <v>1346</v>
       </c>
@@ -54504,8 +55569,29 @@
       <c r="C1099" s="4">
         <v>1437424</v>
       </c>
-    </row>
-    <row r="1100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1099" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1099">
+        <v>49</v>
+      </c>
+      <c r="F1099" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1099" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1099" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1099" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1099" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
         <v>1347</v>
       </c>
@@ -54515,8 +55601,29 @@
       <c r="C1100" s="4">
         <v>1104204</v>
       </c>
-    </row>
-    <row r="1101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1100" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1100">
+        <v>49</v>
+      </c>
+      <c r="F1100" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1100" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1100" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1100" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1100" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1101" t="s">
         <v>1348</v>
       </c>
@@ -54526,8 +55633,29 @@
       <c r="C1101" s="4">
         <v>1597432</v>
       </c>
-    </row>
-    <row r="1102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1101" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1101">
+        <v>49</v>
+      </c>
+      <c r="F1101" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1101" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1101" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1101" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1101" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1102" t="s">
         <v>1349</v>
       </c>
@@ -54537,8 +55665,29 @@
       <c r="C1102" s="4">
         <v>1107679</v>
       </c>
-    </row>
-    <row r="1103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1102" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1102">
+        <v>49</v>
+      </c>
+      <c r="F1102" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1102" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1102" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1102" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1102" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1103" t="s">
         <v>1350</v>
       </c>
@@ -54548,8 +55697,29 @@
       <c r="C1103" s="4">
         <v>1244832</v>
       </c>
-    </row>
-    <row r="1104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1103" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1103">
+        <v>49</v>
+      </c>
+      <c r="F1103" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1103" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1103" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1103" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1103" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1104" t="s">
         <v>1351</v>
       </c>
@@ -54559,8 +55729,29 @@
       <c r="C1104" s="4">
         <v>1147126</v>
       </c>
-    </row>
-    <row r="1105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1104" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1104">
+        <v>49</v>
+      </c>
+      <c r="F1104" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1104" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1104" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1104" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1104" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1105" t="s">
         <v>1352</v>
       </c>
@@ -54570,8 +55761,29 @@
       <c r="C1105" s="4">
         <v>1231072</v>
       </c>
-    </row>
-    <row r="1106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1105" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1105">
+        <v>43</v>
+      </c>
+      <c r="F1105" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1105" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1105" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1105" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1105" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1106" t="s">
         <v>1353</v>
       </c>
@@ -54581,8 +55793,29 @@
       <c r="C1106" s="4">
         <v>312545</v>
       </c>
-    </row>
-    <row r="1107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1106" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1106">
+        <v>26</v>
+      </c>
+      <c r="F1106" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1106" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1106" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1106" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1106" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
         <v>1354</v>
       </c>
@@ -54592,8 +55825,29 @@
       <c r="C1107" s="4">
         <v>933591</v>
       </c>
-    </row>
-    <row r="1108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1107" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1107">
+        <v>49</v>
+      </c>
+      <c r="F1107" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1107" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1107" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1107" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1107" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
         <v>1355</v>
       </c>
@@ -54603,8 +55857,29 @@
       <c r="C1108" s="4">
         <v>1002169</v>
       </c>
-    </row>
-    <row r="1109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1108" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1108">
+        <v>50</v>
+      </c>
+      <c r="F1108" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1108" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1108" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1108" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1108" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
         <v>1356</v>
       </c>
@@ -54614,8 +55889,29 @@
       <c r="C1109" s="4">
         <v>802464</v>
       </c>
-    </row>
-    <row r="1110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1109" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1109">
+        <v>43</v>
+      </c>
+      <c r="F1109" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1109" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1109" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1109" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1109" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1110" t="s">
         <v>1357</v>
       </c>
@@ -54625,8 +55921,29 @@
       <c r="C1110" s="4">
         <v>336637</v>
       </c>
-    </row>
-    <row r="1111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1110" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1110">
+        <v>25</v>
+      </c>
+      <c r="F1110" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1110" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1110" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1110" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1110" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1111" t="s">
         <v>1358</v>
       </c>
@@ -54636,8 +55953,29 @@
       <c r="C1111" s="4">
         <v>414191</v>
       </c>
-    </row>
-    <row r="1112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1111" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1111">
+        <v>24</v>
+      </c>
+      <c r="F1111" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1111" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1111" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1111" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1111" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1112" t="s">
         <v>1359</v>
       </c>
@@ -54647,8 +55985,29 @@
       <c r="C1112" s="4">
         <v>666111</v>
       </c>
-    </row>
-    <row r="1113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1112" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1112">
+        <v>49</v>
+      </c>
+      <c r="F1112" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1112" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1112" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1112" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1112" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1113" t="s">
         <v>1360</v>
       </c>
@@ -54658,8 +56017,29 @@
       <c r="C1113" s="4">
         <v>787797</v>
       </c>
-    </row>
-    <row r="1114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1113" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1113">
+        <v>49</v>
+      </c>
+      <c r="F1113" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1113" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1113" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1113" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1113" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1114" t="s">
         <v>1361</v>
       </c>
@@ -54669,8 +56049,29 @@
       <c r="C1114" s="4">
         <v>184250</v>
       </c>
-    </row>
-    <row r="1115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1114" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1114">
+        <v>91</v>
+      </c>
+      <c r="F1114" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1114" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1114" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1114" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1114" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
         <v>1362</v>
       </c>
@@ -54680,8 +56081,29 @@
       <c r="C1115" s="4">
         <v>115916</v>
       </c>
-    </row>
-    <row r="1116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1115" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1115">
+        <v>90</v>
+      </c>
+      <c r="F1115" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1115" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1115" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1115" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1115" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
         <v>1363</v>
       </c>
@@ -54691,8 +56113,29 @@
       <c r="C1116" s="4">
         <v>114355</v>
       </c>
-    </row>
-    <row r="1117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1116" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1116">
+        <v>90</v>
+      </c>
+      <c r="F1116" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1116" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1116" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1116" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1116" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
         <v>1364</v>
       </c>
@@ -54702,8 +56145,29 @@
       <c r="C1117" s="4">
         <v>103966</v>
       </c>
-    </row>
-    <row r="1118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1117" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1117">
+        <v>92</v>
+      </c>
+      <c r="F1117" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1117" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1117" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1117" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1117" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1118" t="s">
         <v>1365</v>
       </c>
@@ -54713,8 +56177,29 @@
       <c r="C1118" s="4">
         <v>102173</v>
       </c>
-    </row>
-    <row r="1119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1118" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1118">
+        <v>92</v>
+      </c>
+      <c r="F1118" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1118" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1118" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1118" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1118" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1119" t="s">
         <v>1366</v>
       </c>
@@ -54724,8 +56209,29 @@
       <c r="C1119" s="4">
         <v>134907</v>
       </c>
-    </row>
-    <row r="1120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1119" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1119">
+        <v>91</v>
+      </c>
+      <c r="F1119" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1119" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1119" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1119" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1119" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1120" t="s">
         <v>1367</v>
       </c>
@@ -54735,8 +56241,29 @@
       <c r="C1120" s="4">
         <v>119395</v>
       </c>
-    </row>
-    <row r="1121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1120" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1120">
+        <v>91</v>
+      </c>
+      <c r="F1120" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1120" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1120" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1120" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1120" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
         <v>1368</v>
       </c>
@@ -54746,8 +56273,29 @@
       <c r="C1121" s="4">
         <v>121414</v>
       </c>
-    </row>
-    <row r="1122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1121" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1121">
+        <v>91</v>
+      </c>
+      <c r="F1121" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1121" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1121" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1121" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1121" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1122" t="s">
         <v>1369</v>
       </c>
@@ -54757,8 +56305,29 @@
       <c r="C1122" s="4">
         <v>119931</v>
       </c>
-    </row>
-    <row r="1123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1122" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1122">
+        <v>90</v>
+      </c>
+      <c r="F1122" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1122" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1122" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1122" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1122" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1123" t="s">
         <v>1370</v>
       </c>
@@ -54768,8 +56337,29 @@
       <c r="C1123" s="4">
         <v>119931</v>
       </c>
-    </row>
-    <row r="1124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1123" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1123">
+        <v>90</v>
+      </c>
+      <c r="F1123" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1123" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1123" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1123" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1123" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1124" t="s">
         <v>1371</v>
       </c>
@@ -54779,8 +56369,29 @@
       <c r="C1124" s="4">
         <v>123991</v>
       </c>
-    </row>
-    <row r="1125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1124" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1124">
+        <v>90</v>
+      </c>
+      <c r="F1124" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1124" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1124" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1124" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1124" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1125" t="s">
         <v>1372</v>
       </c>
@@ -54790,8 +56401,29 @@
       <c r="C1125" s="4">
         <v>121192</v>
       </c>
-    </row>
-    <row r="1126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1125" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1125">
+        <v>90</v>
+      </c>
+      <c r="F1125" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1125" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1125" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1125" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1125" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1126" t="s">
         <v>1373</v>
       </c>
@@ -54801,8 +56433,29 @@
       <c r="C1126" s="4">
         <v>120272</v>
       </c>
-    </row>
-    <row r="1127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1126" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1126">
+        <v>90</v>
+      </c>
+      <c r="F1126" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1126" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1126" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1126" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1126" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1127" t="s">
         <v>1374</v>
       </c>
@@ -54812,8 +56465,29 @@
       <c r="C1127" s="4">
         <v>118439</v>
       </c>
-    </row>
-    <row r="1128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1127" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1127">
+        <v>90</v>
+      </c>
+      <c r="F1127" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1127" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1127" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1127" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1127" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1128" t="s">
         <v>1375</v>
       </c>
@@ -54823,8 +56497,29 @@
       <c r="C1128" s="4">
         <v>922116</v>
       </c>
-    </row>
-    <row r="1129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1128" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1128">
+        <v>91</v>
+      </c>
+      <c r="F1128" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1128" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1128" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1128" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1128" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1129" t="s">
         <v>1376</v>
       </c>
@@ -54834,8 +56529,29 @@
       <c r="C1129" s="4">
         <v>380503</v>
       </c>
-    </row>
-    <row r="1130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1129" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1129">
+        <v>91</v>
+      </c>
+      <c r="F1129" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1129" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1129" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1129" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1129" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1130" t="s">
         <v>1377</v>
       </c>
@@ -54845,8 +56561,11 @@
       <c r="C1130" s="4">
         <v>241337</v>
       </c>
-    </row>
-    <row r="1131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E1130" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
         <v>1378</v>
       </c>
@@ -54856,8 +56575,29 @@
       <c r="C1131" s="4">
         <v>233715</v>
       </c>
-    </row>
-    <row r="1132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1131" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1131">
+        <v>33</v>
+      </c>
+      <c r="F1131" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1131" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1131" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1131" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1131" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1132" t="s">
         <v>1379</v>
       </c>
@@ -54867,8 +56607,29 @@
       <c r="C1132" s="4">
         <v>232871</v>
       </c>
-    </row>
-    <row r="1133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1132" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1132">
+        <v>33</v>
+      </c>
+      <c r="F1132" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1132" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1132" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1132" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1132" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1133" t="s">
         <v>1380</v>
       </c>
@@ -54878,8 +56639,11 @@
       <c r="C1133" s="4">
         <v>419334</v>
       </c>
-    </row>
-    <row r="1134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E1133" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1134" t="s">
         <v>1381</v>
       </c>
@@ -54889,8 +56653,29 @@
       <c r="C1134" s="4">
         <v>380503</v>
       </c>
-    </row>
-    <row r="1135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1134" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1134">
+        <v>91</v>
+      </c>
+      <c r="F1134" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1134" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1134" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1134" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1134" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1135" t="s">
         <v>1382</v>
       </c>
@@ -54900,8 +56685,29 @@
       <c r="C1135" s="4">
         <v>269577</v>
       </c>
-    </row>
-    <row r="1136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1135" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1135">
+        <v>121</v>
+      </c>
+      <c r="F1135" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1135" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1135" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1135" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1135" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1136" t="s">
         <v>1383</v>
       </c>
@@ -54911,8 +56717,29 @@
       <c r="C1136" s="4">
         <v>1328484</v>
       </c>
-    </row>
-    <row r="1137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1136" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1136">
+        <v>212</v>
+      </c>
+      <c r="F1136" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1136" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1136" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1136" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1136" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1137" t="s">
         <v>1384</v>
       </c>
@@ -54922,8 +56749,29 @@
       <c r="C1137" s="4">
         <v>2402745</v>
       </c>
-    </row>
-    <row r="1138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1137" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1137">
+        <v>188</v>
+      </c>
+      <c r="F1137" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1137" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1137" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1137" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1137" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1138" t="s">
         <v>1385</v>
       </c>
@@ -54933,8 +56781,29 @@
       <c r="C1138" s="4">
         <v>4153928</v>
       </c>
-    </row>
-    <row r="1139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1138" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1138">
+        <v>484</v>
+      </c>
+      <c r="F1138" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1138" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1138" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1138" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1138" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1139" t="s">
         <v>1386</v>
       </c>
@@ -54944,8 +56813,29 @@
       <c r="C1139" s="4">
         <v>212960</v>
       </c>
-    </row>
-    <row r="1140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1139" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1139">
+        <v>41</v>
+      </c>
+      <c r="F1139" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1139" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1139" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1139" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1139" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1140" t="s">
         <v>1387</v>
       </c>
@@ -54955,8 +56845,29 @@
       <c r="C1140" s="4">
         <v>175772</v>
       </c>
-    </row>
-    <row r="1141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1140" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1140">
+        <v>41</v>
+      </c>
+      <c r="F1140" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1140" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1140" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1140" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1140" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1141" t="s">
         <v>1388</v>
       </c>
@@ -54966,8 +56877,29 @@
       <c r="C1141" s="4">
         <v>205204</v>
       </c>
-    </row>
-    <row r="1142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1141" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1141">
+        <v>41</v>
+      </c>
+      <c r="F1141" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1141" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1141" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1141" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1141" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1142" t="s">
         <v>1389</v>
       </c>
@@ -54977,8 +56909,29 @@
       <c r="C1142" s="4">
         <v>315850</v>
       </c>
-    </row>
-    <row r="1143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1142" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1142">
+        <v>41</v>
+      </c>
+      <c r="F1142" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1142" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1142" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1142" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1142" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1143" t="s">
         <v>1390</v>
       </c>
@@ -54988,8 +56941,29 @@
       <c r="C1143" s="4">
         <v>360127</v>
       </c>
-    </row>
-    <row r="1144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1143" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1143">
+        <v>41</v>
+      </c>
+      <c r="F1143" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1143" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1143" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1143" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1143" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1144" t="s">
         <v>1391</v>
       </c>
@@ -54999,8 +56973,29 @@
       <c r="C1144" s="4">
         <v>78162</v>
       </c>
-    </row>
-    <row r="1145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1144" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1144">
+        <v>41</v>
+      </c>
+      <c r="F1144" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1144" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1144" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1144" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1144" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1145" t="s">
         <v>1392</v>
       </c>
@@ -55010,8 +57005,29 @@
       <c r="C1145" s="4">
         <v>1911</v>
       </c>
-    </row>
-    <row r="1146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1145" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1145">
+        <v>21</v>
+      </c>
+      <c r="F1145" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1145" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1145" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1145" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1145" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1146" t="s">
         <v>1393</v>
       </c>
@@ -55021,8 +57037,29 @@
       <c r="C1146" s="4">
         <v>192819</v>
       </c>
-    </row>
-    <row r="1147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1146" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1146">
+        <v>30</v>
+      </c>
+      <c r="F1146" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1146" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1146" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1146" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1146" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1147" t="s">
         <v>1394</v>
       </c>
@@ -55032,8 +57069,29 @@
       <c r="C1147" s="4">
         <v>140076</v>
       </c>
-    </row>
-    <row r="1148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1147" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1147">
+        <v>32</v>
+      </c>
+      <c r="F1147" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1147" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1147" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1147" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1147" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1148" t="s">
         <v>1395</v>
       </c>
@@ -55043,8 +57101,14 @@
       <c r="C1148" s="4">
         <v>198828</v>
       </c>
-    </row>
-    <row r="1149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E1148" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1148" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1149" t="s">
         <v>1396</v>
       </c>
@@ -55054,8 +57118,14 @@
       <c r="C1149" s="4">
         <v>495086</v>
       </c>
-    </row>
-    <row r="1150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E1149" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1149" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1150" t="s">
         <v>1397</v>
       </c>
@@ -55065,8 +57135,29 @@
       <c r="C1150" s="4">
         <v>129154</v>
       </c>
-    </row>
-    <row r="1151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1150" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1150">
+        <v>33</v>
+      </c>
+      <c r="F1150" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1150" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1150" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1150" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1150" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1151" t="s">
         <v>1398</v>
       </c>
@@ -55076,8 +57167,29 @@
       <c r="C1151" s="4">
         <v>481034</v>
       </c>
-    </row>
-    <row r="1152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1151" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1151">
+        <v>33</v>
+      </c>
+      <c r="F1151" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1151" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1151" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1151" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1151" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1152" t="s">
         <v>1399</v>
       </c>
@@ -55087,8 +57199,29 @@
       <c r="C1152" s="4">
         <v>1578016</v>
       </c>
-    </row>
-    <row r="1153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1152" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1152">
+        <v>91</v>
+      </c>
+      <c r="F1152" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1152" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1152" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1152" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1152" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1153" t="s">
         <v>1400</v>
       </c>
@@ -55098,8 +57231,29 @@
       <c r="C1153" s="4">
         <v>1879615</v>
       </c>
-    </row>
-    <row r="1154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1153" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1153">
+        <v>62</v>
+      </c>
+      <c r="F1153" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1153" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1153" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1153" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1153" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1154" t="s">
         <v>1401</v>
       </c>
@@ -55109,8 +57263,29 @@
       <c r="C1154" s="4">
         <v>5619883</v>
       </c>
-    </row>
-    <row r="1155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1154" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1154">
+        <v>393</v>
+      </c>
+      <c r="F1154" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1154" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1154" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1154" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1154" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1155" t="s">
         <v>1402</v>
       </c>
@@ -55120,8 +57295,29 @@
       <c r="C1155" s="4">
         <v>1466510</v>
       </c>
-    </row>
-    <row r="1156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1155" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1155">
+        <v>61</v>
+      </c>
+      <c r="F1155" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1155" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1155" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1155" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1155" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1156" t="s">
         <v>1403</v>
       </c>
@@ -55131,8 +57327,29 @@
       <c r="C1156" s="4">
         <v>2982483</v>
       </c>
-    </row>
-    <row r="1157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1156" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1156">
+        <v>200</v>
+      </c>
+      <c r="F1156" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1156" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1156" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1156" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1156" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1157" t="s">
         <v>1404</v>
       </c>
@@ -55142,8 +57359,29 @@
       <c r="C1157" s="4">
         <v>1247919</v>
       </c>
-    </row>
-    <row r="1158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1157" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1157">
+        <v>92</v>
+      </c>
+      <c r="F1157" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1157" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1157" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1157" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1157" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1158" t="s">
         <v>1405</v>
       </c>
@@ -55153,8 +57391,29 @@
       <c r="C1158" s="4">
         <v>3099362</v>
       </c>
-    </row>
-    <row r="1159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1158" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1158">
+        <v>91</v>
+      </c>
+      <c r="F1158" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1158" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1158" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1158" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1158" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1159" t="s">
         <v>1406</v>
       </c>
@@ -55164,8 +57423,29 @@
       <c r="C1159" s="4">
         <v>3208052</v>
       </c>
-    </row>
-    <row r="1160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1159" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1159">
+        <v>91</v>
+      </c>
+      <c r="F1159" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1159" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1159" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1159" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1159" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1160" t="s">
         <v>1407</v>
       </c>
@@ -55175,8 +57455,29 @@
       <c r="C1160" s="4">
         <v>1477350</v>
       </c>
-    </row>
-    <row r="1161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1160" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1160">
+        <v>91</v>
+      </c>
+      <c r="F1160" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1160" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1160" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1160" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1160" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1161" t="s">
         <v>1408</v>
       </c>
@@ -55185,6 +57486,27 @@
       </c>
       <c r="C1161" s="4">
         <v>2327897</v>
+      </c>
+      <c r="D1161" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1161">
+        <v>91</v>
+      </c>
+      <c r="F1161" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1161" t="s">
+        <v>919</v>
+      </c>
+      <c r="H1161" t="s">
+        <v>919</v>
+      </c>
+      <c r="I1161" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J1161" t="s">
+        <v>1446</v>
       </c>
     </row>
   </sheetData>
@@ -55266,7 +57588,7 @@
         <v>1409</v>
       </c>
       <c r="B8" s="5">
-        <v>149</v>
+        <v>248</v>
       </c>
       <c r="C8" s="5">
         <v>256</v>
@@ -55277,7 +57599,7 @@
         <v>989</v>
       </c>
       <c r="B9" s="5">
-        <v>1051</v>
+        <v>1150</v>
       </c>
       <c r="C9" s="5">
         <v>1160</v>

--- a/image manifest.xlsx
+++ b/image manifest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Github\CS-Graphics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890FBC49-6F10-4CE1-8407-38AFAD25E180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6EEC027-C783-4DB6-860C-107F07F3C5E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="2415" windowWidth="21600" windowHeight="12795" xr2:uid="{620D0F7A-D0D3-4EA0-8A4D-C0BB25CE06A6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{620D0F7A-D0D3-4EA0-8A4D-C0BB25CE06A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4592,7 +4592,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="User" refreshedDate="46273.60544201389" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1160" xr:uid="{475285A3-2F52-4B23-B5E6-6919749F1CF6}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="User" refreshedDate="46273.653569212962" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1160" xr:uid="{475285A3-2F52-4B23-B5E6-6919749F1CF6}">
   <cacheSource type="worksheet">
     <worksheetSource name="Table1"/>
   </cacheSource>
@@ -19394,12 +19394,12 @@
     <x v="4"/>
     <n v="1328484"/>
     <s v="SELF"/>
-    <n v="1001"/>
+    <n v="212"/>
     <s v="Yes"/>
     <s v="No"/>
     <s v="No"/>
     <s v="Video"/>
-    <s v="Tutorial 1 TODO"/>
+    <s v="Tutorial 1 TODO (fixed)"/>
     <m/>
   </r>
   <r>
@@ -19407,7 +19407,7 @@
     <x v="4"/>
     <n v="2402745"/>
     <s v="SELF"/>
-    <n v="1501"/>
+    <n v="188"/>
     <s v="Yes"/>
     <s v="No"/>
     <s v="No"/>

--- a/image manifest.xlsx
+++ b/image manifest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Github\CS-Graphics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6EEC027-C783-4DB6-860C-107F07F3C5E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD999E39-EF47-4172-920C-DA109F2DBD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{620D0F7A-D0D3-4EA0-8A4D-C0BB25CE06A6}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4561,7 +4561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -4569,7 +4569,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19731,7 +19730,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FA313DB3-B760-4691-87E1-B5DF4E7F9B43}" name="PivotTable3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FA313DB3-B760-4691-87E1-B5DF4E7F9B43}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -49469,7 +49468,7 @@
         <v>1132</v>
       </c>
       <c r="E906">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F906" t="s">
         <v>914</v>
@@ -49501,7 +49500,7 @@
         <v>1132</v>
       </c>
       <c r="E907">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F907" t="s">
         <v>914</v>
@@ -49533,7 +49532,7 @@
         <v>1132</v>
       </c>
       <c r="E908">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F908" t="s">
         <v>914</v>
@@ -49565,7 +49564,7 @@
         <v>1132</v>
       </c>
       <c r="E909">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F909" t="s">
         <v>914</v>
@@ -49597,7 +49596,7 @@
         <v>1132</v>
       </c>
       <c r="E910">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F910" t="s">
         <v>914</v>
@@ -49629,7 +49628,7 @@
         <v>1132</v>
       </c>
       <c r="E911">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F911" t="s">
         <v>914</v>
@@ -49661,7 +49660,7 @@
         <v>1132</v>
       </c>
       <c r="E912">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F912" t="s">
         <v>914</v>
@@ -49693,7 +49692,7 @@
         <v>1132</v>
       </c>
       <c r="E913">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F913" t="s">
         <v>914</v>
@@ -49725,7 +49724,7 @@
         <v>1132</v>
       </c>
       <c r="E914">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F914" t="s">
         <v>914</v>
@@ -49757,7 +49756,7 @@
         <v>1132</v>
       </c>
       <c r="E915">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F915" t="s">
         <v>914</v>
@@ -49789,7 +49788,7 @@
         <v>1132</v>
       </c>
       <c r="E916">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F916" t="s">
         <v>914</v>
@@ -49821,7 +49820,7 @@
         <v>1132</v>
       </c>
       <c r="E917">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F917" t="s">
         <v>914</v>
@@ -49853,7 +49852,7 @@
         <v>1132</v>
       </c>
       <c r="E918">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F918" t="s">
         <v>914</v>
@@ -49885,7 +49884,7 @@
         <v>1132</v>
       </c>
       <c r="E919">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F919" t="s">
         <v>914</v>
@@ -49917,7 +49916,7 @@
         <v>1132</v>
       </c>
       <c r="E920">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F920" t="s">
         <v>914</v>
@@ -49949,7 +49948,7 @@
         <v>1132</v>
       </c>
       <c r="E921">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F921" t="s">
         <v>914</v>
@@ -49981,7 +49980,7 @@
         <v>1132</v>
       </c>
       <c r="E922">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F922" t="s">
         <v>914</v>
@@ -50013,7 +50012,7 @@
         <v>1132</v>
       </c>
       <c r="E923">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F923" t="s">
         <v>914</v>
@@ -50045,7 +50044,7 @@
         <v>1132</v>
       </c>
       <c r="E924">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F924" t="s">
         <v>914</v>
@@ -50077,7 +50076,7 @@
         <v>1132</v>
       </c>
       <c r="E925">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F925" t="s">
         <v>914</v>
@@ -50109,7 +50108,7 @@
         <v>1132</v>
       </c>
       <c r="E926">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F926" t="s">
         <v>914</v>
@@ -50141,7 +50140,7 @@
         <v>1132</v>
       </c>
       <c r="E927">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F927" t="s">
         <v>914</v>
@@ -50173,7 +50172,7 @@
         <v>1132</v>
       </c>
       <c r="E928">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F928" t="s">
         <v>914</v>
@@ -50205,7 +50204,7 @@
         <v>1132</v>
       </c>
       <c r="E929">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F929" t="s">
         <v>914</v>
@@ -50237,7 +50236,7 @@
         <v>1132</v>
       </c>
       <c r="E930">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F930" t="s">
         <v>914</v>
@@ -50269,7 +50268,7 @@
         <v>1132</v>
       </c>
       <c r="E931">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F931" t="s">
         <v>914</v>
@@ -50301,7 +50300,7 @@
         <v>1132</v>
       </c>
       <c r="E932">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F932" t="s">
         <v>914</v>
@@ -50333,7 +50332,7 @@
         <v>1132</v>
       </c>
       <c r="E933">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F933" t="s">
         <v>914</v>
@@ -50365,7 +50364,7 @@
         <v>1132</v>
       </c>
       <c r="E934">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F934" t="s">
         <v>914</v>
@@ -50397,7 +50396,7 @@
         <v>1132</v>
       </c>
       <c r="E935">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F935" t="s">
         <v>914</v>
@@ -50429,7 +50428,7 @@
         <v>1132</v>
       </c>
       <c r="E936">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F936" t="s">
         <v>914</v>
@@ -50461,7 +50460,7 @@
         <v>1132</v>
       </c>
       <c r="E937">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F937" t="s">
         <v>914</v>
@@ -50493,7 +50492,7 @@
         <v>1132</v>
       </c>
       <c r="E938">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F938" t="s">
         <v>914</v>
@@ -50525,7 +50524,7 @@
         <v>1132</v>
       </c>
       <c r="E939">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F939" t="s">
         <v>914</v>
@@ -50557,7 +50556,7 @@
         <v>1132</v>
       </c>
       <c r="E940">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F940" t="s">
         <v>914</v>
@@ -50589,7 +50588,7 @@
         <v>1132</v>
       </c>
       <c r="E941">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F941" t="s">
         <v>914</v>
@@ -50621,7 +50620,7 @@
         <v>1132</v>
       </c>
       <c r="E942">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F942" t="s">
         <v>914</v>
@@ -50653,7 +50652,7 @@
         <v>1132</v>
       </c>
       <c r="E943">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F943" t="s">
         <v>914</v>
@@ -50685,7 +50684,7 @@
         <v>1132</v>
       </c>
       <c r="E944">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F944" t="s">
         <v>914</v>
@@ -50717,7 +50716,7 @@
         <v>1132</v>
       </c>
       <c r="E945">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F945" t="s">
         <v>914</v>
@@ -50749,7 +50748,7 @@
         <v>1132</v>
       </c>
       <c r="E946">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F946" t="s">
         <v>914</v>
@@ -50781,7 +50780,7 @@
         <v>1132</v>
       </c>
       <c r="E947">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F947" t="s">
         <v>914</v>
@@ -50813,7 +50812,7 @@
         <v>1132</v>
       </c>
       <c r="E948">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F948" t="s">
         <v>914</v>
@@ -50845,7 +50844,7 @@
         <v>1132</v>
       </c>
       <c r="E949">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F949" t="s">
         <v>914</v>
@@ -50877,7 +50876,7 @@
         <v>1132</v>
       </c>
       <c r="E950">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F950" t="s">
         <v>914</v>
@@ -50909,7 +50908,7 @@
         <v>1132</v>
       </c>
       <c r="E951">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F951" t="s">
         <v>914</v>
@@ -50941,7 +50940,7 @@
         <v>1132</v>
       </c>
       <c r="E952">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F952" t="s">
         <v>914</v>
@@ -50973,7 +50972,7 @@
         <v>1132</v>
       </c>
       <c r="E953">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F953" t="s">
         <v>914</v>
@@ -51005,7 +51004,7 @@
         <v>1132</v>
       </c>
       <c r="E954">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F954" t="s">
         <v>914</v>
@@ -51037,7 +51036,7 @@
         <v>1132</v>
       </c>
       <c r="E955">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F955" t="s">
         <v>914</v>
@@ -51069,7 +51068,7 @@
         <v>1132</v>
       </c>
       <c r="E956">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F956" t="s">
         <v>914</v>
@@ -51101,7 +51100,7 @@
         <v>1132</v>
       </c>
       <c r="E957">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F957" t="s">
         <v>914</v>
@@ -51133,7 +51132,7 @@
         <v>1132</v>
       </c>
       <c r="E958">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F958" t="s">
         <v>914</v>
@@ -51165,7 +51164,7 @@
         <v>1132</v>
       </c>
       <c r="E959">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F959" t="s">
         <v>914</v>
@@ -51197,7 +51196,7 @@
         <v>1132</v>
       </c>
       <c r="E960">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F960" t="s">
         <v>914</v>
@@ -51229,7 +51228,7 @@
         <v>1132</v>
       </c>
       <c r="E961">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F961" t="s">
         <v>914</v>
@@ -51261,7 +51260,7 @@
         <v>1132</v>
       </c>
       <c r="E962">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F962" t="s">
         <v>914</v>
@@ -51293,7 +51292,7 @@
         <v>1132</v>
       </c>
       <c r="E963">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F963" t="s">
         <v>914</v>
@@ -51325,7 +51324,7 @@
         <v>1132</v>
       </c>
       <c r="E964">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F964" t="s">
         <v>914</v>
@@ -51357,7 +51356,7 @@
         <v>1132</v>
       </c>
       <c r="E965">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F965" t="s">
         <v>914</v>
@@ -51389,7 +51388,7 @@
         <v>1132</v>
       </c>
       <c r="E966">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F966" t="s">
         <v>914</v>
@@ -51421,7 +51420,7 @@
         <v>1132</v>
       </c>
       <c r="E967">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F967" t="s">
         <v>914</v>
@@ -51453,7 +51452,7 @@
         <v>1132</v>
       </c>
       <c r="E968">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F968" t="s">
         <v>914</v>
@@ -51485,7 +51484,7 @@
         <v>1132</v>
       </c>
       <c r="E969">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F969" t="s">
         <v>914</v>
@@ -51517,7 +51516,7 @@
         <v>1132</v>
       </c>
       <c r="E970">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F970" t="s">
         <v>914</v>
@@ -51549,7 +51548,7 @@
         <v>1132</v>
       </c>
       <c r="E971">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F971" t="s">
         <v>914</v>
@@ -51581,7 +51580,7 @@
         <v>1132</v>
       </c>
       <c r="E972">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F972" t="s">
         <v>914</v>
@@ -51613,7 +51612,7 @@
         <v>1132</v>
       </c>
       <c r="E973">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F973" t="s">
         <v>914</v>
@@ -51645,7 +51644,7 @@
         <v>1132</v>
       </c>
       <c r="E974">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F974" t="s">
         <v>914</v>
@@ -51677,7 +51676,7 @@
         <v>1132</v>
       </c>
       <c r="E975">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F975" t="s">
         <v>914</v>
@@ -51709,7 +51708,7 @@
         <v>1132</v>
       </c>
       <c r="E976">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F976" t="s">
         <v>914</v>
@@ -51741,7 +51740,7 @@
         <v>1132</v>
       </c>
       <c r="E977">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F977" t="s">
         <v>914</v>
@@ -51773,7 +51772,7 @@
         <v>1132</v>
       </c>
       <c r="E978">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F978" t="s">
         <v>914</v>
@@ -51805,7 +51804,7 @@
         <v>1132</v>
       </c>
       <c r="E979">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F979" t="s">
         <v>914</v>
@@ -51837,7 +51836,7 @@
         <v>1132</v>
       </c>
       <c r="E980">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F980" t="s">
         <v>914</v>
@@ -51869,7 +51868,7 @@
         <v>1132</v>
       </c>
       <c r="E981">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F981" t="s">
         <v>914</v>
@@ -51901,7 +51900,7 @@
         <v>1132</v>
       </c>
       <c r="E982">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F982" t="s">
         <v>914</v>
@@ -51933,7 +51932,7 @@
         <v>1132</v>
       </c>
       <c r="E983">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F983" t="s">
         <v>914</v>
@@ -51965,7 +51964,7 @@
         <v>1132</v>
       </c>
       <c r="E984">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F984" t="s">
         <v>914</v>
@@ -51997,7 +51996,7 @@
         <v>1132</v>
       </c>
       <c r="E985">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F985" t="s">
         <v>914</v>
@@ -52029,7 +52028,7 @@
         <v>1132</v>
       </c>
       <c r="E986">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F986" t="s">
         <v>914</v>
@@ -52061,7 +52060,7 @@
         <v>1132</v>
       </c>
       <c r="E987">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F987" t="s">
         <v>914</v>
@@ -52093,7 +52092,7 @@
         <v>1132</v>
       </c>
       <c r="E988">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F988" t="s">
         <v>914</v>
@@ -52125,7 +52124,7 @@
         <v>1132</v>
       </c>
       <c r="E989">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F989" t="s">
         <v>914</v>
@@ -52157,7 +52156,7 @@
         <v>1132</v>
       </c>
       <c r="E990">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F990" t="s">
         <v>914</v>
@@ -52189,7 +52188,7 @@
         <v>1132</v>
       </c>
       <c r="E991">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F991" t="s">
         <v>914</v>
@@ -52221,7 +52220,7 @@
         <v>1132</v>
       </c>
       <c r="E992">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F992" t="s">
         <v>914</v>
@@ -52253,7 +52252,7 @@
         <v>1132</v>
       </c>
       <c r="E993">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F993" t="s">
         <v>914</v>
@@ -52285,7 +52284,7 @@
         <v>1132</v>
       </c>
       <c r="E994">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F994" t="s">
         <v>914</v>
@@ -52317,7 +52316,7 @@
         <v>1132</v>
       </c>
       <c r="E995">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F995" t="s">
         <v>914</v>
@@ -52349,7 +52348,7 @@
         <v>1132</v>
       </c>
       <c r="E996">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F996" t="s">
         <v>914</v>
@@ -52381,7 +52380,7 @@
         <v>1132</v>
       </c>
       <c r="E997">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F997" t="s">
         <v>914</v>
@@ -52413,7 +52412,7 @@
         <v>1132</v>
       </c>
       <c r="E998">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F998" t="s">
         <v>914</v>
@@ -52445,7 +52444,7 @@
         <v>1132</v>
       </c>
       <c r="E999">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F999" t="s">
         <v>914</v>
@@ -52477,7 +52476,7 @@
         <v>1132</v>
       </c>
       <c r="E1000">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1000" t="s">
         <v>914</v>
@@ -52509,7 +52508,7 @@
         <v>1132</v>
       </c>
       <c r="E1001">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1001" t="s">
         <v>914</v>
@@ -52541,7 +52540,7 @@
         <v>1132</v>
       </c>
       <c r="E1002">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1002" t="s">
         <v>914</v>
@@ -52573,7 +52572,7 @@
         <v>1132</v>
       </c>
       <c r="E1003">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1003" t="s">
         <v>914</v>
@@ -52605,7 +52604,7 @@
         <v>1132</v>
       </c>
       <c r="E1004">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1004" t="s">
         <v>914</v>
@@ -52637,7 +52636,7 @@
         <v>1132</v>
       </c>
       <c r="E1005">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1005" t="s">
         <v>914</v>
@@ -52669,7 +52668,7 @@
         <v>1132</v>
       </c>
       <c r="E1006">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1006" t="s">
         <v>914</v>
@@ -52701,7 +52700,7 @@
         <v>1132</v>
       </c>
       <c r="E1007">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F1007" t="s">
         <v>914</v>
@@ -52733,7 +52732,7 @@
         <v>1132</v>
       </c>
       <c r="E1008">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1008" t="s">
         <v>914</v>
@@ -52765,7 +52764,7 @@
         <v>1132</v>
       </c>
       <c r="E1009">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1009" t="s">
         <v>914</v>
@@ -52797,7 +52796,7 @@
         <v>1132</v>
       </c>
       <c r="E1010">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1010" t="s">
         <v>914</v>
@@ -52829,7 +52828,7 @@
         <v>1132</v>
       </c>
       <c r="E1011">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1011" t="s">
         <v>914</v>
@@ -52861,7 +52860,7 @@
         <v>1132</v>
       </c>
       <c r="E1012">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1012" t="s">
         <v>914</v>
@@ -52893,7 +52892,7 @@
         <v>1132</v>
       </c>
       <c r="E1013">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1013" t="s">
         <v>914</v>
@@ -52925,7 +52924,7 @@
         <v>1132</v>
       </c>
       <c r="E1014">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1014" t="s">
         <v>914</v>
@@ -52957,7 +52956,7 @@
         <v>1132</v>
       </c>
       <c r="E1015">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1015" t="s">
         <v>914</v>
@@ -52989,7 +52988,7 @@
         <v>1132</v>
       </c>
       <c r="E1016">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1016" t="s">
         <v>914</v>
@@ -53021,7 +53020,7 @@
         <v>1132</v>
       </c>
       <c r="E1017">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1017" t="s">
         <v>914</v>
@@ -53053,7 +53052,7 @@
         <v>1132</v>
       </c>
       <c r="E1018">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1018" t="s">
         <v>914</v>
@@ -53085,7 +53084,7 @@
         <v>1132</v>
       </c>
       <c r="E1019">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1019" t="s">
         <v>914</v>
@@ -53117,7 +53116,7 @@
         <v>1132</v>
       </c>
       <c r="E1020">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1020" t="s">
         <v>914</v>
@@ -53149,7 +53148,7 @@
         <v>1132</v>
       </c>
       <c r="E1021">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1021" t="s">
         <v>914</v>
@@ -53181,7 +53180,7 @@
         <v>1132</v>
       </c>
       <c r="E1022">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1022" t="s">
         <v>914</v>
@@ -53213,7 +53212,7 @@
         <v>1132</v>
       </c>
       <c r="E1023">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1023" t="s">
         <v>914</v>
@@ -53245,7 +53244,7 @@
         <v>1132</v>
       </c>
       <c r="E1024">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1024" t="s">
         <v>914</v>
@@ -53277,7 +53276,7 @@
         <v>1132</v>
       </c>
       <c r="E1025">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1025" t="s">
         <v>914</v>
@@ -53309,7 +53308,7 @@
         <v>1132</v>
       </c>
       <c r="E1026">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1026" t="s">
         <v>914</v>
@@ -53341,7 +53340,7 @@
         <v>1132</v>
       </c>
       <c r="E1027">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1027" t="s">
         <v>914</v>
@@ -53373,7 +53372,7 @@
         <v>1132</v>
       </c>
       <c r="E1028">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1028" t="s">
         <v>914</v>
@@ -53405,7 +53404,7 @@
         <v>1132</v>
       </c>
       <c r="E1029">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1029" t="s">
         <v>914</v>
@@ -53437,7 +53436,7 @@
         <v>1132</v>
       </c>
       <c r="E1030">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1030" t="s">
         <v>914</v>
@@ -53469,7 +53468,7 @@
         <v>1132</v>
       </c>
       <c r="E1031">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1031" t="s">
         <v>914</v>
@@ -53501,7 +53500,7 @@
         <v>1132</v>
       </c>
       <c r="E1032">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1032" t="s">
         <v>914</v>
@@ -53533,7 +53532,7 @@
         <v>1132</v>
       </c>
       <c r="E1033">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1033" t="s">
         <v>914</v>
@@ -53565,7 +53564,7 @@
         <v>1132</v>
       </c>
       <c r="E1034">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1034" t="s">
         <v>914</v>
@@ -53597,7 +53596,7 @@
         <v>1132</v>
       </c>
       <c r="E1035">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1035" t="s">
         <v>914</v>
@@ -53629,7 +53628,7 @@
         <v>1132</v>
       </c>
       <c r="E1036">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1036" t="s">
         <v>914</v>
@@ -53661,7 +53660,7 @@
         <v>1132</v>
       </c>
       <c r="E1037">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1037" t="s">
         <v>914</v>
@@ -53693,7 +53692,7 @@
         <v>1132</v>
       </c>
       <c r="E1038">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1038" t="s">
         <v>914</v>
@@ -53725,7 +53724,7 @@
         <v>1132</v>
       </c>
       <c r="E1039">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1039" t="s">
         <v>914</v>
@@ -53757,7 +53756,7 @@
         <v>1132</v>
       </c>
       <c r="E1040">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1040" t="s">
         <v>914</v>
@@ -53789,7 +53788,7 @@
         <v>1132</v>
       </c>
       <c r="E1041">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1041" t="s">
         <v>914</v>
@@ -53821,7 +53820,7 @@
         <v>1132</v>
       </c>
       <c r="E1042">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1042" t="s">
         <v>914</v>
@@ -53853,7 +53852,7 @@
         <v>1132</v>
       </c>
       <c r="E1043">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1043" t="s">
         <v>914</v>
@@ -53885,7 +53884,7 @@
         <v>1132</v>
       </c>
       <c r="E1044">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1044" t="s">
         <v>914</v>
@@ -53917,7 +53916,7 @@
         <v>1132</v>
       </c>
       <c r="E1045">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1045" t="s">
         <v>914</v>
@@ -53949,7 +53948,7 @@
         <v>1132</v>
       </c>
       <c r="E1046">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1046" t="s">
         <v>914</v>
@@ -53981,7 +53980,7 @@
         <v>1132</v>
       </c>
       <c r="E1047">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1047" t="s">
         <v>914</v>
@@ -54013,7 +54012,7 @@
         <v>1132</v>
       </c>
       <c r="E1048">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1048" t="s">
         <v>914</v>
@@ -54045,7 +54044,7 @@
         <v>1132</v>
       </c>
       <c r="E1049">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1049" t="s">
         <v>914</v>
@@ -54077,7 +54076,7 @@
         <v>1132</v>
       </c>
       <c r="E1050">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1050" t="s">
         <v>914</v>
@@ -54109,7 +54108,7 @@
         <v>1132</v>
       </c>
       <c r="E1051">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1051" t="s">
         <v>914</v>
@@ -54141,7 +54140,7 @@
         <v>1132</v>
       </c>
       <c r="E1052">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1052" t="s">
         <v>914</v>
@@ -54173,7 +54172,7 @@
         <v>1132</v>
       </c>
       <c r="E1053">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1053" t="s">
         <v>914</v>
@@ -54205,7 +54204,7 @@
         <v>1132</v>
       </c>
       <c r="E1054">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1054" t="s">
         <v>914</v>
@@ -54251,7 +54250,7 @@
         <v>1132</v>
       </c>
       <c r="E1056">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1056" t="s">
         <v>914</v>
@@ -54297,7 +54296,7 @@
         <v>1132</v>
       </c>
       <c r="E1058">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="F1058" t="s">
         <v>914</v>
@@ -54329,7 +54328,7 @@
         <v>1132</v>
       </c>
       <c r="E1059">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1059" t="s">
         <v>914</v>
@@ -54361,7 +54360,7 @@
         <v>1132</v>
       </c>
       <c r="E1060">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1060" t="s">
         <v>914</v>
@@ -54407,7 +54406,7 @@
         <v>1132</v>
       </c>
       <c r="E1062">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F1062" t="s">
         <v>914</v>
@@ -54439,7 +54438,7 @@
         <v>1132</v>
       </c>
       <c r="E1063">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F1063" t="s">
         <v>914</v>
@@ -54471,7 +54470,7 @@
         <v>1132</v>
       </c>
       <c r="E1064">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1064" t="s">
         <v>914</v>
@@ -54503,7 +54502,7 @@
         <v>1132</v>
       </c>
       <c r="E1065">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1065" t="s">
         <v>914</v>
@@ -54535,7 +54534,7 @@
         <v>1132</v>
       </c>
       <c r="E1066">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1066" t="s">
         <v>914</v>
@@ -54567,7 +54566,7 @@
         <v>1132</v>
       </c>
       <c r="E1067">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1067" t="s">
         <v>914</v>
@@ -54599,7 +54598,7 @@
         <v>1132</v>
       </c>
       <c r="E1068">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1068" t="s">
         <v>914</v>
@@ -54631,7 +54630,7 @@
         <v>1132</v>
       </c>
       <c r="E1069">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1069" t="s">
         <v>914</v>
@@ -54663,7 +54662,7 @@
         <v>1132</v>
       </c>
       <c r="E1070">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1070" t="s">
         <v>914</v>
@@ -54759,7 +54758,7 @@
         <v>1132</v>
       </c>
       <c r="E1073">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F1073" t="s">
         <v>914</v>
@@ -54791,7 +54790,7 @@
         <v>1132</v>
       </c>
       <c r="E1074">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1074" t="s">
         <v>914</v>
@@ -54823,7 +54822,7 @@
         <v>1132</v>
       </c>
       <c r="E1075">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F1075" t="s">
         <v>914</v>
@@ -54855,7 +54854,7 @@
         <v>1132</v>
       </c>
       <c r="E1076">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F1076" t="s">
         <v>914</v>
@@ -54887,7 +54886,7 @@
         <v>1132</v>
       </c>
       <c r="E1077">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1077" t="s">
         <v>914</v>
@@ -54919,7 +54918,7 @@
         <v>1132</v>
       </c>
       <c r="E1078">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1078" t="s">
         <v>914</v>
@@ -54951,7 +54950,7 @@
         <v>1132</v>
       </c>
       <c r="E1079">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1079" t="s">
         <v>914</v>
@@ -54983,7 +54982,7 @@
         <v>1132</v>
       </c>
       <c r="E1080">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1080" t="s">
         <v>914</v>
@@ -55015,7 +55014,7 @@
         <v>1132</v>
       </c>
       <c r="E1081">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F1081" t="s">
         <v>914</v>
@@ -55047,7 +55046,7 @@
         <v>1132</v>
       </c>
       <c r="E1082">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F1082" t="s">
         <v>914</v>
@@ -55079,7 +55078,7 @@
         <v>1132</v>
       </c>
       <c r="E1083">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F1083" t="s">
         <v>914</v>
@@ -55111,7 +55110,7 @@
         <v>1132</v>
       </c>
       <c r="E1084">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F1084" t="s">
         <v>914</v>
@@ -55143,7 +55142,7 @@
         <v>1132</v>
       </c>
       <c r="E1085">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1085" t="s">
         <v>914</v>
@@ -55175,7 +55174,7 @@
         <v>1132</v>
       </c>
       <c r="E1086">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1086" t="s">
         <v>914</v>
@@ -55207,7 +55206,7 @@
         <v>1132</v>
       </c>
       <c r="E1087">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F1087" t="s">
         <v>914</v>
@@ -55239,7 +55238,7 @@
         <v>1132</v>
       </c>
       <c r="E1088">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F1088" t="s">
         <v>914</v>
@@ -55271,7 +55270,7 @@
         <v>1132</v>
       </c>
       <c r="E1089">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F1089" t="s">
         <v>914</v>
@@ -55317,7 +55316,7 @@
         <v>1132</v>
       </c>
       <c r="E1091">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F1091" t="s">
         <v>914</v>
@@ -55349,7 +55348,7 @@
         <v>1132</v>
       </c>
       <c r="E1092">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F1092" t="s">
         <v>914</v>
@@ -55381,7 +55380,7 @@
         <v>1132</v>
       </c>
       <c r="E1093">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1093" t="s">
         <v>914</v>
@@ -55413,7 +55412,7 @@
         <v>1132</v>
       </c>
       <c r="E1094">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F1094" t="s">
         <v>914</v>
@@ -55445,7 +55444,7 @@
         <v>1132</v>
       </c>
       <c r="E1095">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1095" t="s">
         <v>914</v>
@@ -55477,7 +55476,7 @@
         <v>1132</v>
       </c>
       <c r="E1096">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1096" t="s">
         <v>914</v>
@@ -55509,7 +55508,7 @@
         <v>1132</v>
       </c>
       <c r="E1097">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1097" t="s">
         <v>914</v>
@@ -55541,7 +55540,7 @@
         <v>1132</v>
       </c>
       <c r="E1098">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1098" t="s">
         <v>914</v>
@@ -55573,7 +55572,7 @@
         <v>1132</v>
       </c>
       <c r="E1099">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1099" t="s">
         <v>914</v>
@@ -55605,7 +55604,7 @@
         <v>1132</v>
       </c>
       <c r="E1100">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1100" t="s">
         <v>914</v>
@@ -55637,7 +55636,7 @@
         <v>1132</v>
       </c>
       <c r="E1101">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1101" t="s">
         <v>914</v>
@@ -55669,7 +55668,7 @@
         <v>1132</v>
       </c>
       <c r="E1102">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1102" t="s">
         <v>914</v>
@@ -55701,7 +55700,7 @@
         <v>1132</v>
       </c>
       <c r="E1103">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1103" t="s">
         <v>914</v>
@@ -55733,7 +55732,7 @@
         <v>1132</v>
       </c>
       <c r="E1104">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1104" t="s">
         <v>914</v>
@@ -55765,7 +55764,7 @@
         <v>1132</v>
       </c>
       <c r="E1105">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F1105" t="s">
         <v>914</v>
@@ -55797,7 +55796,7 @@
         <v>1132</v>
       </c>
       <c r="E1106">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F1106" t="s">
         <v>914</v>
@@ -55829,7 +55828,7 @@
         <v>1132</v>
       </c>
       <c r="E1107">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1107" t="s">
         <v>914</v>
@@ -55861,7 +55860,7 @@
         <v>1132</v>
       </c>
       <c r="E1108">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F1108" t="s">
         <v>914</v>
@@ -55893,7 +55892,7 @@
         <v>1132</v>
       </c>
       <c r="E1109">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F1109" t="s">
         <v>914</v>
@@ -55925,7 +55924,7 @@
         <v>1132</v>
       </c>
       <c r="E1110">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F1110" t="s">
         <v>914</v>
@@ -55957,7 +55956,7 @@
         <v>1132</v>
       </c>
       <c r="E1111">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F1111" t="s">
         <v>914</v>
@@ -55989,7 +55988,7 @@
         <v>1132</v>
       </c>
       <c r="E1112">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1112" t="s">
         <v>914</v>
@@ -56021,7 +56020,7 @@
         <v>1132</v>
       </c>
       <c r="E1113">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1113" t="s">
         <v>914</v>
@@ -56053,7 +56052,7 @@
         <v>1132</v>
       </c>
       <c r="E1114">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1114" t="s">
         <v>914</v>
@@ -56085,7 +56084,7 @@
         <v>1132</v>
       </c>
       <c r="E1115">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F1115" t="s">
         <v>914</v>
@@ -56117,7 +56116,7 @@
         <v>1132</v>
       </c>
       <c r="E1116">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F1116" t="s">
         <v>914</v>
@@ -56149,7 +56148,7 @@
         <v>1132</v>
       </c>
       <c r="E1117">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F1117" t="s">
         <v>914</v>
@@ -56181,7 +56180,7 @@
         <v>1132</v>
       </c>
       <c r="E1118">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F1118" t="s">
         <v>914</v>
@@ -56213,7 +56212,7 @@
         <v>1132</v>
       </c>
       <c r="E1119">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1119" t="s">
         <v>914</v>
@@ -56245,7 +56244,7 @@
         <v>1132</v>
       </c>
       <c r="E1120">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1120" t="s">
         <v>914</v>
@@ -56277,7 +56276,7 @@
         <v>1132</v>
       </c>
       <c r="E1121">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1121" t="s">
         <v>914</v>
@@ -56309,7 +56308,7 @@
         <v>1132</v>
       </c>
       <c r="E1122">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F1122" t="s">
         <v>914</v>
@@ -56341,7 +56340,7 @@
         <v>1132</v>
       </c>
       <c r="E1123">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F1123" t="s">
         <v>914</v>
@@ -56373,7 +56372,7 @@
         <v>1132</v>
       </c>
       <c r="E1124">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F1124" t="s">
         <v>914</v>
@@ -56405,7 +56404,7 @@
         <v>1132</v>
       </c>
       <c r="E1125">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F1125" t="s">
         <v>914</v>
@@ -56437,7 +56436,7 @@
         <v>1132</v>
       </c>
       <c r="E1126">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F1126" t="s">
         <v>914</v>
@@ -56469,7 +56468,7 @@
         <v>1132</v>
       </c>
       <c r="E1127">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F1127" t="s">
         <v>914</v>
@@ -56501,7 +56500,7 @@
         <v>1132</v>
       </c>
       <c r="E1128">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1128" t="s">
         <v>914</v>
@@ -56533,7 +56532,7 @@
         <v>1132</v>
       </c>
       <c r="E1129">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1129" t="s">
         <v>914</v>
@@ -56579,7 +56578,7 @@
         <v>1132</v>
       </c>
       <c r="E1131">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F1131" t="s">
         <v>914</v>
@@ -56611,7 +56610,7 @@
         <v>1132</v>
       </c>
       <c r="E1132">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F1132" t="s">
         <v>914</v>
@@ -56657,7 +56656,7 @@
         <v>1132</v>
       </c>
       <c r="E1134">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1134" t="s">
         <v>914</v>
@@ -56689,7 +56688,7 @@
         <v>1132</v>
       </c>
       <c r="E1135">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1135" t="s">
         <v>914</v>
@@ -56785,7 +56784,7 @@
         <v>1132</v>
       </c>
       <c r="E1138">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F1138" t="s">
         <v>914</v>
@@ -56817,7 +56816,7 @@
         <v>1132</v>
       </c>
       <c r="E1139">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F1139" t="s">
         <v>914</v>
@@ -56849,7 +56848,7 @@
         <v>1132</v>
       </c>
       <c r="E1140">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F1140" t="s">
         <v>914</v>
@@ -56881,7 +56880,7 @@
         <v>1132</v>
       </c>
       <c r="E1141">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F1141" t="s">
         <v>914</v>
@@ -56913,7 +56912,7 @@
         <v>1132</v>
       </c>
       <c r="E1142">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F1142" t="s">
         <v>914</v>
@@ -56945,7 +56944,7 @@
         <v>1132</v>
       </c>
       <c r="E1143">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F1143" t="s">
         <v>914</v>
@@ -56977,7 +56976,7 @@
         <v>1132</v>
       </c>
       <c r="E1144">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F1144" t="s">
         <v>914</v>
@@ -57009,7 +57008,7 @@
         <v>1132</v>
       </c>
       <c r="E1145">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F1145" t="s">
         <v>914</v>
@@ -57041,7 +57040,7 @@
         <v>1132</v>
       </c>
       <c r="E1146">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F1146" t="s">
         <v>914</v>
@@ -57073,7 +57072,7 @@
         <v>1132</v>
       </c>
       <c r="E1147">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F1147" t="s">
         <v>914</v>
@@ -57139,7 +57138,7 @@
         <v>1132</v>
       </c>
       <c r="E1150">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F1150" t="s">
         <v>914</v>
@@ -57171,7 +57170,7 @@
         <v>1132</v>
       </c>
       <c r="E1151">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F1151" t="s">
         <v>914</v>
@@ -57203,7 +57202,7 @@
         <v>1132</v>
       </c>
       <c r="E1152">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1152" t="s">
         <v>914</v>
@@ -57235,7 +57234,7 @@
         <v>1132</v>
       </c>
       <c r="E1153">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F1153" t="s">
         <v>914</v>
@@ -57267,7 +57266,7 @@
         <v>1132</v>
       </c>
       <c r="E1154">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F1154" t="s">
         <v>914</v>
@@ -57299,7 +57298,7 @@
         <v>1132</v>
       </c>
       <c r="E1155">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F1155" t="s">
         <v>914</v>
@@ -57331,7 +57330,7 @@
         <v>1132</v>
       </c>
       <c r="E1156">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F1156" t="s">
         <v>914</v>
@@ -57363,7 +57362,7 @@
         <v>1132</v>
       </c>
       <c r="E1157">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F1157" t="s">
         <v>914</v>
@@ -57395,7 +57394,7 @@
         <v>1132</v>
       </c>
       <c r="E1158">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1158" t="s">
         <v>914</v>
@@ -57427,7 +57426,7 @@
         <v>1132</v>
       </c>
       <c r="E1159">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1159" t="s">
         <v>914</v>
@@ -57459,7 +57458,7 @@
         <v>1132</v>
       </c>
       <c r="E1160">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1160" t="s">
         <v>914</v>
@@ -57491,7 +57490,7 @@
         <v>1132</v>
       </c>
       <c r="E1161">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F1161" t="s">
         <v>914</v>
@@ -57543,10 +57542,10 @@
       <c r="A4" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>746</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4">
         <v>746</v>
       </c>
     </row>
@@ -57554,10 +57553,10 @@
       <c r="A5" s="3" t="s">
         <v>992</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5">
         <v>1</v>
       </c>
     </row>
@@ -57565,10 +57564,10 @@
       <c r="A6" s="3" t="s">
         <v>990</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>150</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6">
         <v>152</v>
       </c>
     </row>
@@ -57576,10 +57575,10 @@
       <c r="A7" s="3" t="s">
         <v>1145</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>5</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7">
         <v>5</v>
       </c>
     </row>
@@ -57587,10 +57586,10 @@
       <c r="A8" s="3" t="s">
         <v>1409</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>248</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8">
         <v>256</v>
       </c>
     </row>
@@ -57598,10 +57597,10 @@
       <c r="A9" s="3" t="s">
         <v>989</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>1150</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9">
         <v>1160</v>
       </c>
     </row>
